--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -2128,7 +2128,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134240323</v>
+        <v>134238487</v>
       </c>
       <c r="B15" t="n">
         <v>96766</v>
@@ -2159,17 +2159,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kroppasjön, Kroppasjön, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>336314</v>
+        <v>336180</v>
       </c>
       <c r="R15" t="n">
-        <v>6442640</v>
+        <v>6442460</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134238487</v>
+        <v>134240323</v>
       </c>
       <c r="B16" t="n">
         <v>96766</v>
@@ -2266,17 +2266,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Kroppasjön, Kroppasjön, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>336180</v>
+        <v>336314</v>
       </c>
       <c r="R16" t="n">
-        <v>6442460</v>
+        <v>6442640</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2447,6 +2447,118 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134284341</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>336371</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6442654</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -791,27 +791,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134237890</v>
+        <v>134238236</v>
       </c>
       <c r="B3" t="n">
-        <v>58349</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,7 +822,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>336216</v>
+        <v>336201</v>
       </c>
       <c r="R3" t="n">
-        <v>6442415</v>
+        <v>6442457</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,27 +903,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134238236</v>
+        <v>134237890</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>58349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,7 +934,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>336201</v>
+        <v>336216</v>
       </c>
       <c r="R4" t="n">
-        <v>6442457</v>
+        <v>6442415</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1018,7 @@
         <v>134238983</v>
       </c>
       <c r="B5" t="n">
-        <v>96406</v>
+        <v>96408</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>134237167</v>
       </c>
       <c r="B6" t="n">
-        <v>96406</v>
+        <v>96408</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134240231</v>
+        <v>134238353</v>
       </c>
       <c r="B10" t="n">
-        <v>96766</v>
+        <v>96768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,17 +1593,21 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hönsekungens, Hönsekungens, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>336290</v>
+        <v>336190</v>
       </c>
       <c r="R10" t="n">
-        <v>6442639</v>
+        <v>6442473</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1635,7 +1639,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1645,7 +1649,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,53 +1681,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134240000</v>
+        <v>134240231</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>96768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>336249</v>
+        <v>336290</v>
       </c>
       <c r="R11" t="n">
-        <v>6442581</v>
+        <v>6442639</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,7 +1751,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,7 +1761,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134240692</v>
+        <v>134240000</v>
       </c>
       <c r="B12" t="n">
         <v>57972</v>
@@ -1820,17 +1824,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroppasjön, Ale-Skövde, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>336220</v>
+        <v>336249</v>
       </c>
       <c r="R12" t="n">
-        <v>6442621</v>
+        <v>6442581</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1873,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,49 +1900,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134238353</v>
+        <v>134240692</v>
       </c>
       <c r="B13" t="n">
-        <v>96766</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>336190</v>
+        <v>336220</v>
       </c>
       <c r="R13" t="n">
-        <v>6442473</v>
+        <v>6442621</v>
       </c>
       <c r="S13" t="n">
         <v>6</v>
@@ -1970,7 +1975,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,12 +1985,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Större kudde</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,7 +2015,7 @@
         <v>134238268</v>
       </c>
       <c r="B14" t="n">
-        <v>96406</v>
+        <v>96408</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>134238487</v>
       </c>
       <c r="B15" t="n">
-        <v>96766</v>
+        <v>96768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>134240323</v>
       </c>
       <c r="B16" t="n">
-        <v>96766</v>
+        <v>96768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>134238818</v>
       </c>
       <c r="B17" t="n">
-        <v>96406</v>
+        <v>96408</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134236906</v>
+        <v>134238254</v>
       </c>
       <c r="B7" t="n">
         <v>57972</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>336150</v>
+        <v>336203</v>
       </c>
       <c r="R7" t="n">
-        <v>6442359</v>
+        <v>6442477</v>
       </c>
       <c r="S7" t="n">
         <v>6</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134238254</v>
+        <v>134236906</v>
       </c>
       <c r="B8" t="n">
         <v>57972</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>336203</v>
+        <v>336150</v>
       </c>
       <c r="R8" t="n">
-        <v>6442477</v>
+        <v>6442359</v>
       </c>
       <c r="S8" t="n">
         <v>6</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134240000</v>
+        <v>134240692</v>
       </c>
       <c r="B12" t="n">
         <v>57972</v>
@@ -1824,17 +1824,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>336249</v>
+        <v>336220</v>
       </c>
       <c r="R12" t="n">
-        <v>6442581</v>
+        <v>6442621</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,7 +1900,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134240692</v>
+        <v>134240000</v>
       </c>
       <c r="B13" t="n">
         <v>57972</v>
@@ -1936,17 +1936,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kroppasjön, Ale-Skövde, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>336220</v>
+        <v>336249</v>
       </c>
       <c r="R13" t="n">
-        <v>6442621</v>
+        <v>6442581</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>134238983</v>
       </c>
       <c r="B5" t="n">
-        <v>96408</v>
+        <v>96409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>134237167</v>
       </c>
       <c r="B6" t="n">
-        <v>96408</v>
+        <v>96409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134238254</v>
+        <v>134236906</v>
       </c>
       <c r="B7" t="n">
         <v>57972</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>336203</v>
+        <v>336150</v>
       </c>
       <c r="R7" t="n">
-        <v>6442477</v>
+        <v>6442359</v>
       </c>
       <c r="S7" t="n">
         <v>6</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134236906</v>
+        <v>134238254</v>
       </c>
       <c r="B8" t="n">
         <v>57972</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>336150</v>
+        <v>336203</v>
       </c>
       <c r="R8" t="n">
-        <v>6442359</v>
+        <v>6442477</v>
       </c>
       <c r="S8" t="n">
         <v>6</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1565,37 +1565,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134238353</v>
+        <v>134240000</v>
       </c>
       <c r="B10" t="n">
-        <v>96768</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1604,13 +1605,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>336190</v>
+        <v>336249</v>
       </c>
       <c r="R10" t="n">
-        <v>6442473</v>
+        <v>6442581</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1639,7 +1640,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1649,12 +1650,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Större kudde</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,7 +1680,7 @@
         <v>134240231</v>
       </c>
       <c r="B11" t="n">
-        <v>96768</v>
+        <v>96769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,38 +1896,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134240000</v>
+        <v>134238353</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>96769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1940,13 +1935,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>336249</v>
+        <v>336190</v>
       </c>
       <c r="R13" t="n">
-        <v>6442581</v>
+        <v>6442473</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1975,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1985,7 +1980,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,7 +2015,7 @@
         <v>134238268</v>
       </c>
       <c r="B14" t="n">
-        <v>96408</v>
+        <v>96409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134238487</v>
+        <v>134240323</v>
       </c>
       <c r="B15" t="n">
-        <v>96768</v>
+        <v>96769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2159,17 +2159,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Kroppasjön, Kroppasjön, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>336180</v>
+        <v>336314</v>
       </c>
       <c r="R15" t="n">
-        <v>6442460</v>
+        <v>6442640</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134240323</v>
+        <v>134238487</v>
       </c>
       <c r="B16" t="n">
-        <v>96768</v>
+        <v>96769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,17 +2266,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kroppasjön, Kroppasjön, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>336314</v>
+        <v>336180</v>
       </c>
       <c r="R16" t="n">
-        <v>6442640</v>
+        <v>6442460</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,7 +2345,7 @@
         <v>134238818</v>
       </c>
       <c r="B17" t="n">
-        <v>96408</v>
+        <v>96409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -791,27 +791,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134238236</v>
+        <v>134237890</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>58349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,7 +822,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>336201</v>
+        <v>336216</v>
       </c>
       <c r="R3" t="n">
-        <v>6442457</v>
+        <v>6442415</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,27 +903,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134237890</v>
+        <v>134238236</v>
       </c>
       <c r="B4" t="n">
-        <v>58349</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,7 +934,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>336216</v>
+        <v>336201</v>
       </c>
       <c r="R4" t="n">
-        <v>6442415</v>
+        <v>6442457</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134236906</v>
+        <v>134238254</v>
       </c>
       <c r="B7" t="n">
         <v>57972</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>336150</v>
+        <v>336203</v>
       </c>
       <c r="R7" t="n">
-        <v>6442359</v>
+        <v>6442477</v>
       </c>
       <c r="S7" t="n">
         <v>6</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134238254</v>
+        <v>134236906</v>
       </c>
       <c r="B8" t="n">
         <v>57972</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>336203</v>
+        <v>336150</v>
       </c>
       <c r="R8" t="n">
-        <v>6442477</v>
+        <v>6442359</v>
       </c>
       <c r="S8" t="n">
         <v>6</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1565,7 +1565,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134240000</v>
+        <v>134240692</v>
       </c>
       <c r="B10" t="n">
         <v>57972</v>
@@ -1601,17 +1601,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>336249</v>
+        <v>336220</v>
       </c>
       <c r="R10" t="n">
-        <v>6442581</v>
+        <v>6442621</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,48 +1677,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134240231</v>
+        <v>134240000</v>
       </c>
       <c r="B11" t="n">
-        <v>96769</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hönsekungens, Hönsekungens, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>336290</v>
+        <v>336249</v>
       </c>
       <c r="R11" t="n">
-        <v>6442639</v>
+        <v>6442581</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,7 +1762,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,50 +1789,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134240692</v>
+        <v>134240231</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>96769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroppasjön, Ale-Skövde, Vg</t>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>336220</v>
+        <v>336290</v>
       </c>
       <c r="R12" t="n">
-        <v>6442621</v>
+        <v>6442639</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2128,7 +2128,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134240323</v>
+        <v>134238487</v>
       </c>
       <c r="B15" t="n">
         <v>96769</v>
@@ -2159,17 +2159,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kroppasjön, Kroppasjön, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>336314</v>
+        <v>336180</v>
       </c>
       <c r="R15" t="n">
-        <v>6442640</v>
+        <v>6442460</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134238487</v>
+        <v>134240323</v>
       </c>
       <c r="B16" t="n">
         <v>96769</v>
@@ -2266,17 +2266,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Kroppasjön, Kroppasjön, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>336180</v>
+        <v>336314</v>
       </c>
       <c r="R16" t="n">
-        <v>6442460</v>
+        <v>6442640</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>134238983</v>
       </c>
       <c r="B5" t="n">
-        <v>96409</v>
+        <v>96416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>134237167</v>
       </c>
       <c r="B6" t="n">
-        <v>96409</v>
+        <v>96416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134238254</v>
+        <v>134236906</v>
       </c>
       <c r="B7" t="n">
         <v>57972</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>336203</v>
+        <v>336150</v>
       </c>
       <c r="R7" t="n">
-        <v>6442477</v>
+        <v>6442359</v>
       </c>
       <c r="S7" t="n">
         <v>6</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134236906</v>
+        <v>134238254</v>
       </c>
       <c r="B8" t="n">
         <v>57972</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>336150</v>
+        <v>336203</v>
       </c>
       <c r="R8" t="n">
-        <v>6442359</v>
+        <v>6442477</v>
       </c>
       <c r="S8" t="n">
         <v>6</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1565,7 +1565,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134240692</v>
+        <v>134240000</v>
       </c>
       <c r="B10" t="n">
         <v>57972</v>
@@ -1601,17 +1601,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kroppasjön, Ale-Skövde, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>336220</v>
+        <v>336249</v>
       </c>
       <c r="R10" t="n">
-        <v>6442621</v>
+        <v>6442581</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,53 +1677,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134240000</v>
+        <v>134240231</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>96776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>336249</v>
+        <v>336290</v>
       </c>
       <c r="R11" t="n">
-        <v>6442581</v>
+        <v>6442639</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,7 +1747,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,7 +1757,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,45 +1784,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134240231</v>
+        <v>134240692</v>
       </c>
       <c r="B12" t="n">
-        <v>96769</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hönsekungens, Hönsekungens, Vg</t>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>336290</v>
+        <v>336220</v>
       </c>
       <c r="R12" t="n">
-        <v>6442639</v>
+        <v>6442621</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,7 +1899,7 @@
         <v>134238353</v>
       </c>
       <c r="B13" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>134238268</v>
       </c>
       <c r="B14" t="n">
-        <v>96409</v>
+        <v>96416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134238487</v>
+        <v>134240323</v>
       </c>
       <c r="B15" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2159,17 +2159,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Kroppasjön, Kroppasjön, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>336180</v>
+        <v>336314</v>
       </c>
       <c r="R15" t="n">
-        <v>6442460</v>
+        <v>6442640</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134240323</v>
+        <v>134238487</v>
       </c>
       <c r="B16" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,17 +2266,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kroppasjön, Kroppasjön, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>336314</v>
+        <v>336180</v>
       </c>
       <c r="R16" t="n">
-        <v>6442640</v>
+        <v>6442460</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,7 +2345,7 @@
         <v>134238818</v>
       </c>
       <c r="B17" t="n">
-        <v>96409</v>
+        <v>96416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134239926</v>
+        <v>134238353</v>
       </c>
       <c r="B2" t="n">
-        <v>58349</v>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,24 +708,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>336172</v>
+        <v>336190</v>
       </c>
       <c r="R2" t="n">
-        <v>6442583</v>
+        <v>6442473</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +759,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134237890</v>
+        <v>134238487</v>
       </c>
       <c r="B3" t="n">
-        <v>58349</v>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,42 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>336216</v>
+        <v>336180</v>
       </c>
       <c r="R3" t="n">
-        <v>6442415</v>
+        <v>6442460</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,53 +898,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134238236</v>
+        <v>134240231</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>96783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>336201</v>
+        <v>336290</v>
       </c>
       <c r="R4" t="n">
-        <v>6442457</v>
+        <v>6442639</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134238983</v>
+        <v>134240323</v>
       </c>
       <c r="B5" t="n">
-        <v>96416</v>
+        <v>96783</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Kroppasjön, Kroppasjön, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>336157</v>
+        <v>336314</v>
       </c>
       <c r="R5" t="n">
-        <v>6442543</v>
+        <v>6442640</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134237167</v>
+        <v>134451739</v>
       </c>
       <c r="B6" t="n">
-        <v>96416</v>
+        <v>96783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,37 +1123,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>336193</v>
+        <v>336397</v>
       </c>
       <c r="R6" t="n">
-        <v>6442380</v>
+        <v>6442584</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,22 +1177,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,53 +1219,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134236906</v>
+        <v>134452977</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>96783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Kroppasjön, Kroppasjön, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>336150</v>
+        <v>336398</v>
       </c>
       <c r="R7" t="n">
-        <v>6442359</v>
+        <v>6442631</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,22 +1284,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera kuddar a 20-40cm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,65 +1319,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134238254</v>
+        <v>134237167</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>96423</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>336203</v>
+        <v>336193</v>
       </c>
       <c r="R8" t="n">
-        <v>6442477</v>
+        <v>6442380</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,7 +1401,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1411,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,38 +1438,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134238282</v>
+        <v>134238268</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>96423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1493,13 +1482,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>336201</v>
+        <v>336200</v>
       </c>
       <c r="R9" t="n">
-        <v>6442468</v>
+        <v>6442475</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1528,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1527,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,53 +1554,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134240000</v>
+        <v>134238818</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>96423</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>336249</v>
+        <v>336158</v>
       </c>
       <c r="R10" t="n">
-        <v>6442581</v>
+        <v>6442532</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134240231</v>
+        <v>134238983</v>
       </c>
       <c r="B11" t="n">
-        <v>96776</v>
+        <v>96423</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,34 +1672,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hönsekungens, Hönsekungens, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>336290</v>
+        <v>336157</v>
       </c>
       <c r="R11" t="n">
-        <v>6442639</v>
+        <v>6442543</v>
       </c>
       <c r="S11" t="n">
         <v>6</v>
@@ -1747,7 +1731,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,7 +1741,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,53 +1768,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134240692</v>
+        <v>134451725</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>96423</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroppasjön, Ale-Skövde, Vg</t>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>336220</v>
+        <v>336399</v>
       </c>
       <c r="R12" t="n">
-        <v>6442621</v>
+        <v>6442585</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1854,22 +1833,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134238353</v>
+        <v>134452206</v>
       </c>
       <c r="B13" t="n">
-        <v>96776</v>
+        <v>96423</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,41 +1886,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>336190</v>
+        <v>336381</v>
       </c>
       <c r="R13" t="n">
-        <v>6442473</v>
+        <v>6442582</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1965,27 +1940,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Större kudde</t>
+          <t>Mattor med västlig hakmossa</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,10 +1987,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134238268</v>
+        <v>134236906</v>
       </c>
       <c r="B14" t="n">
-        <v>96416</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,31 +1998,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2056,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>336200</v>
+        <v>336150</v>
       </c>
       <c r="R14" t="n">
-        <v>6442475</v>
+        <v>6442359</v>
       </c>
       <c r="S14" t="n">
         <v>6</v>
@@ -2091,7 +2062,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2101,7 +2072,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,10 +2099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134240323</v>
+        <v>134238236</v>
       </c>
       <c r="B15" t="n">
-        <v>96776</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2139,37 +2110,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kroppasjön, Kroppasjön, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>336314</v>
+        <v>336201</v>
       </c>
       <c r="R15" t="n">
-        <v>6442640</v>
+        <v>6442457</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2174,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2184,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,10 +2211,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134238487</v>
+        <v>134238254</v>
       </c>
       <c r="B16" t="n">
-        <v>96776</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,37 +2222,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>336180</v>
+        <v>336203</v>
       </c>
       <c r="R16" t="n">
-        <v>6442460</v>
+        <v>6442477</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2305,7 +2286,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2315,7 +2296,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2342,10 +2323,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134238818</v>
+        <v>134238282</v>
       </c>
       <c r="B17" t="n">
-        <v>96416</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2353,34 +2334,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>336158</v>
+        <v>336201</v>
       </c>
       <c r="R17" t="n">
-        <v>6442532</v>
+        <v>6442468</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2412,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2422,7 +2408,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,14 +2435,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134284341</v>
+        <v>134240000</v>
       </c>
       <c r="B18" t="n">
         <v>57972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2485,17 +2471,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kroppasjön, Ale-Skövde, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>336371</v>
+        <v>336249</v>
       </c>
       <c r="R18" t="n">
-        <v>6442654</v>
+        <v>6442581</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2519,22 +2505,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2549,15 +2535,1054 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134240692</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>336220</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6442621</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134284341</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>336371</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6442654</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Linus Lundin</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Linus Lundin</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134452745</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>336390</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6442691</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Känsla av avledande beteende,  då den både visade sig, fög och dröjde sig kvar bland träden</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134454095</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kroppasjön, Kroppasjön, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>336398</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6442631</v>
+      </c>
+      <c r="S22" t="n">
+        <v>6</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134238932</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58231</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102980</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ladusvala</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hirundo rustica</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hålan, Hålan, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>336168</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6442532</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134237890</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hålan, Hålan, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>336216</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6442415</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134239926</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hålan, Hålan, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>336172</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6442583</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134451182</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>336301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6442331</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Flög upp och beskådade mig när jag passerade.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134452917</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>336371</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6442787</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3470,54 +3470,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134452917</v>
+        <v>134500384</v>
       </c>
       <c r="B27" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kroppasjön, Ale-Skövde, Vg</t>
+          <t>Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>336371</v>
+        <v>336316</v>
       </c>
       <c r="R27" t="n">
-        <v>6442787</v>
+        <v>6442596</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3544,22 +3539,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Inspelad i fält med Audiomoth, flera inspelningar på samma ställe mellan 11-17 juni, så arten verkar stationär på lokalen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3574,15 +3574,131 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134452917</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>336371</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6442787</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134237167</v>
+        <v>134615703</v>
       </c>
       <c r="B8" t="n">
-        <v>96423</v>
+        <v>96783</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,37 +1342,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>336193</v>
+        <v>336420</v>
       </c>
       <c r="R8" t="n">
-        <v>6442380</v>
+        <v>6442604</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1396,22 +1396,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera stora kuddar varav största ca 1m i diameter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,22 +1431,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134238268</v>
+        <v>134617768</v>
       </c>
       <c r="B9" t="n">
-        <v>96423</v>
+        <v>97862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,46 +1454,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Kroppasjön, Kroppasjön, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>336200</v>
+        <v>336382</v>
       </c>
       <c r="R9" t="n">
-        <v>6442475</v>
+        <v>6442809</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,22 +1508,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,19 +1538,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134238818</v>
+        <v>134237167</v>
       </c>
       <c r="B10" t="n">
         <v>96423</v>
@@ -1589,13 +1585,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>336158</v>
+        <v>336193</v>
       </c>
       <c r="R10" t="n">
-        <v>6442532</v>
+        <v>6442380</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1624,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,7 +1657,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134238983</v>
+        <v>134238268</v>
       </c>
       <c r="B11" t="n">
         <v>96423</v>
@@ -1689,17 +1685,26 @@
           <t>(Hedw.) Warnst.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>336157</v>
+        <v>336200</v>
       </c>
       <c r="R11" t="n">
-        <v>6442543</v>
+        <v>6442475</v>
       </c>
       <c r="S11" t="n">
         <v>6</v>
@@ -1731,7 +1736,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1741,7 +1746,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,7 +1773,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134451725</v>
+        <v>134238818</v>
       </c>
       <c r="B12" t="n">
         <v>96423</v>
@@ -1799,17 +1804,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hönsekungens, Hönsekungens, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>336399</v>
+        <v>336158</v>
       </c>
       <c r="R12" t="n">
-        <v>6442585</v>
+        <v>6442532</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1833,22 +1838,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,7 +1880,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134452206</v>
+        <v>134238983</v>
       </c>
       <c r="B13" t="n">
         <v>96423</v>
@@ -1906,17 +1911,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hönsekungens, Hönsekungens, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>336381</v>
+        <v>336157</v>
       </c>
       <c r="R13" t="n">
-        <v>6442582</v>
+        <v>6442543</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1940,27 +1945,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mattor med västlig hakmossa</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,10 +1987,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134236906</v>
+        <v>134451725</v>
       </c>
       <c r="B14" t="n">
-        <v>57972</v>
+        <v>96423</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,42 +1998,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>336150</v>
+        <v>336399</v>
       </c>
       <c r="R14" t="n">
-        <v>6442359</v>
+        <v>6442585</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2057,22 +2052,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2099,10 +2094,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134238236</v>
+        <v>134452206</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>96423</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,42 +2105,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>336201</v>
+        <v>336381</v>
       </c>
       <c r="R15" t="n">
-        <v>6442457</v>
+        <v>6442582</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,22 +2159,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Mattor med västlig hakmossa</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2211,7 +2206,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134238254</v>
+        <v>134236906</v>
       </c>
       <c r="B16" t="n">
         <v>57972</v>
@@ -2251,10 +2246,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>336203</v>
+        <v>336150</v>
       </c>
       <c r="R16" t="n">
-        <v>6442477</v>
+        <v>6442359</v>
       </c>
       <c r="S16" t="n">
         <v>6</v>
@@ -2286,7 +2281,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2296,7 +2291,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,7 +2318,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134238282</v>
+        <v>134238236</v>
       </c>
       <c r="B17" t="n">
         <v>57972</v>
@@ -2366,7 +2361,7 @@
         <v>336201</v>
       </c>
       <c r="R17" t="n">
-        <v>6442468</v>
+        <v>6442457</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2398,7 +2393,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,7 +2403,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,7 +2430,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134240000</v>
+        <v>134238254</v>
       </c>
       <c r="B18" t="n">
         <v>57972</v>
@@ -2475,13 +2470,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>336249</v>
+        <v>336203</v>
       </c>
       <c r="R18" t="n">
-        <v>6442581</v>
+        <v>6442477</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2510,7 +2505,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2520,7 +2515,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,7 +2542,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134240692</v>
+        <v>134238282</v>
       </c>
       <c r="B19" t="n">
         <v>57972</v>
@@ -2583,17 +2578,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kroppasjön, Ale-Skövde, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>336220</v>
+        <v>336201</v>
       </c>
       <c r="R19" t="n">
-        <v>6442621</v>
+        <v>6442468</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2622,7 +2617,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2632,7 +2627,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,7 +2654,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134284341</v>
+        <v>134240000</v>
       </c>
       <c r="B20" t="n">
         <v>57972</v>
@@ -2695,17 +2690,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kroppasjön, Ale-Skövde, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>336371</v>
+        <v>336249</v>
       </c>
       <c r="R20" t="n">
-        <v>6442654</v>
+        <v>6442581</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2729,22 +2724,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2759,19 +2754,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134452745</v>
+        <v>134240692</v>
       </c>
       <c r="B21" t="n">
         <v>57972</v>
@@ -2802,7 +2797,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2811,13 +2806,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>336390</v>
+        <v>336220</v>
       </c>
       <c r="R21" t="n">
-        <v>6442691</v>
+        <v>6442621</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2841,27 +2836,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Känsla av avledande beteende,  då den både visade sig, fög och dröjde sig kvar bland träden</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,7 +2878,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134454095</v>
+        <v>134284341</v>
       </c>
       <c r="B22" t="n">
         <v>57972</v>
@@ -2919,22 +2909,22 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kroppasjön, Kroppasjön, Vg</t>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>336398</v>
+        <v>336371</v>
       </c>
       <c r="R22" t="n">
-        <v>6442631</v>
+        <v>6442654</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2958,22 +2948,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,54 +2990,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134238932</v>
+        <v>134452745</v>
       </c>
       <c r="B23" t="n">
-        <v>58231</v>
+        <v>57972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102980</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>336168</v>
+        <v>336390</v>
       </c>
       <c r="R23" t="n">
-        <v>6442532</v>
+        <v>6442691</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,22 +3060,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Känsla av avledande beteende,  då den både visade sig, fög och dröjde sig kvar bland träden</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3116,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134237890</v>
+        <v>134454095</v>
       </c>
       <c r="B24" t="n">
-        <v>58349</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3127,16 +3118,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3147,22 +3138,22 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Kroppasjön, Kroppasjön, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>336216</v>
+        <v>336398</v>
       </c>
       <c r="R24" t="n">
-        <v>6442415</v>
+        <v>6442631</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3186,22 +3177,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3216,22 +3207,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134239926</v>
+        <v>134615747</v>
       </c>
       <c r="B25" t="n">
-        <v>58349</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,16 +3230,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3256,29 +3247,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>336172</v>
+        <v>336420</v>
       </c>
       <c r="R25" t="n">
-        <v>6442583</v>
+        <v>6442604</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3302,22 +3289,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,22 +3319,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134451182</v>
+        <v>134624853</v>
       </c>
       <c r="B26" t="n">
-        <v>58461</v>
+        <v>57776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,51 +3342,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103018</v>
+        <v>102118</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hönsekungens, Hönsekungens, Vg</t>
+          <t>Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>336301</v>
+        <v>336316</v>
       </c>
       <c r="R26" t="n">
-        <v>6442331</v>
+        <v>6442596</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3423,27 +3400,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>00:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Flög upp och beskådade mig när jag passerade.</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3458,61 +3430,62 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134500384</v>
+        <v>134624703</v>
       </c>
       <c r="B27" t="n">
-        <v>58136</v>
+        <v>57796</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>102976</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hönsekungens, Vg</t>
+          <t>Hönsakullen 2, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>336316</v>
+        <v>336374</v>
       </c>
       <c r="R27" t="n">
-        <v>6442596</v>
+        <v>6442672</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3539,27 +3512,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Inspelad i fält med Audiomoth, flera inspelningar på samma ställe mellan 11-17 juni, så arten verkar stationär på lokalen.</t>
+          <t>Inspelad i fält med Audiomoth</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3568,6 +3541,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3586,32 +3560,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134452917</v>
+        <v>134238932</v>
       </c>
       <c r="B28" t="n">
-        <v>58131</v>
+        <v>58231</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103023</v>
+        <v>102980</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3621,19 +3595,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroppasjön, Ale-Skövde, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>336371</v>
+        <v>336168</v>
       </c>
       <c r="R28" t="n">
-        <v>6442787</v>
+        <v>6442532</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3660,22 +3634,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,6 +3673,944 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134624437</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58519</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hönsakullen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>336374</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6442672</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134237890</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hålan, Hålan, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>336216</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6442415</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134239926</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hålan, Hålan, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>336172</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6442583</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134451182</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>336301</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6442331</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Flög upp och beskådade mig när jag passerade.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134500384</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hönsekungens, Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>336316</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6442596</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Inspelad i fält med Audiomoth, flera inspelningar på samma ställe mellan 11-17 juni, så arten verkar stationär på lokalen.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134617186</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>336327</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6442801</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Flera stycken observerade med kikare</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134624565</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hönsakullen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>336374</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6442672</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Inspelad på plats med Audiomoth</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134452917</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>336371</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6442787</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4612,6 +4612,128 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134688508</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hålan Lilla Edets kommun , Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>336247</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6442626</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gnagspår på klenare död granstam</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Naturskog, barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134238353</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134238487</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134240231</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134240323</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134451739</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452977</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134615703</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134617768</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1654,6 +1699,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134237167</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1770,6 +1820,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134238268</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1877,6 +1932,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134238818</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,6 +2044,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134238983</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2091,6 +2156,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134451725</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2203,6 +2273,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452206</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2315,6 +2390,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236906</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2427,6 +2507,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134238236</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2539,6 +2624,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134238254</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2651,6 +2741,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134238282</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2763,6 +2858,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134240000</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2875,6 +2975,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134240692</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2987,6 +3092,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134284341</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3104,6 +3214,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452745</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3216,6 +3331,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134454095</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3328,6 +3448,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134615747</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3439,6 +3564,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624853</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3557,6 +3687,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624703</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3673,6 +3808,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134238932</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3792,6 +3932,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624437</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3904,6 +4049,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134237890</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4020,6 +4170,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134239926</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4146,6 +4301,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134451182</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4262,6 +4422,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134500384</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4379,6 +4544,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134617186</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4495,6 +4665,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624565</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4611,6 +4786,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452917</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4733,8 +4913,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134688508</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3456,50 +3456,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134624703</v>
+        <v>134624853</v>
       </c>
       <c r="B26" t="n">
-        <v>57796</v>
+        <v>57781</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102976</v>
+        <v>102118</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hönsakullen 2, Vg</t>
+          <t>Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>336374</v>
+        <v>336316</v>
       </c>
       <c r="R26" t="n">
-        <v>6442672</v>
+        <v>6442596</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3526,27 +3525,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>00:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Inspelad i fält med Audiomoth</t>
+          <t>00:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3555,7 +3549,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3573,60 +3566,56 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134624703</t>
+          <t>https://artportalen.se/Sighting/134624853</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134238932</v>
+        <v>134624703</v>
       </c>
       <c r="B27" t="n">
-        <v>58231</v>
+        <v>57796</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102980</v>
+        <v>102976</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Hönsakullen 2, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>336168</v>
+        <v>336374</v>
       </c>
       <c r="R27" t="n">
-        <v>6442532</v>
+        <v>6442672</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3653,22 +3642,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Inspelad i fält med Audiomoth</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3677,33 +3671,34 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134238932</t>
+          <t>https://artportalen.se/Sighting/134624703</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134624437</v>
+        <v>134238932</v>
       </c>
       <c r="B28" t="n">
-        <v>58519</v>
+        <v>58231</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,21 +3706,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102990</v>
+        <v>102980</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3733,24 +3728,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hönsakullen 2, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>336374</v>
+        <v>336168</v>
       </c>
       <c r="R28" t="n">
-        <v>6442672</v>
+        <v>6442532</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3777,22 +3769,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3807,44 +3799,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134624437</t>
+          <t>https://artportalen.se/Sighting/134238932</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134237890</v>
+        <v>134624437</v>
       </c>
       <c r="B29" t="n">
-        <v>58349</v>
+        <v>58519</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3852,22 +3844,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hålan, Hålan, Vg</t>
+          <t>Hönsakullen 2, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>336216</v>
+        <v>336374</v>
       </c>
       <c r="R29" t="n">
-        <v>6442415</v>
+        <v>6442672</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3894,22 +3893,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3924,24 +3923,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134237890</t>
+          <t>https://artportalen.se/Sighting/134624437</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134239926</v>
+        <v>134237890</v>
       </c>
       <c r="B30" t="n">
         <v>58349</v>
@@ -3969,11 +3968,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -3985,10 +3980,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>336172</v>
+        <v>336216</v>
       </c>
       <c r="R30" t="n">
-        <v>6442583</v>
+        <v>6442415</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4020,7 +4015,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4030,7 +4025,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4056,16 +4051,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134239926</t>
+          <t>https://artportalen.se/Sighting/134237890</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134451182</v>
+        <v>134239926</v>
       </c>
       <c r="B31" t="n">
-        <v>58461</v>
+        <v>58349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,21 +4068,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4095,29 +4090,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hönsekungens, Hönsekungens, Vg</t>
+          <t>Hålan, Hålan, Vg</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>336301</v>
+        <v>336172</v>
       </c>
       <c r="R31" t="n">
-        <v>6442331</v>
+        <v>6442583</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4141,27 +4131,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flög upp och beskådade mig när jag passerade.</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4187,16 +4172,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134451182</t>
+          <t>https://artportalen.se/Sighting/134239926</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134452917</v>
+        <v>134451182</v>
       </c>
       <c r="B32" t="n">
-        <v>58131</v>
+        <v>58461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4204,21 +4189,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103023</v>
+        <v>103018</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4226,24 +4211,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kroppasjön, Ale-Skövde, Vg</t>
+          <t>Hönsekungens, Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>336371</v>
+        <v>336301</v>
       </c>
       <c r="R32" t="n">
-        <v>6442787</v>
+        <v>6442331</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4272,7 +4262,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4282,7 +4272,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Flög upp och beskådade mig när jag passerade.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4308,60 +4303,55 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452917</t>
+          <t>https://artportalen.se/Sighting/134451182</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134688508</v>
+        <v>134500384</v>
       </c>
       <c r="B33" t="n">
-        <v>5201</v>
+        <v>58141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hålan Lilla Edets kommun , Vg</t>
+          <t>Hönsekungens, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>336247</v>
+        <v>336316</v>
       </c>
       <c r="R33" t="n">
-        <v>6442626</v>
+        <v>6442596</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4388,17 +4378,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gnagspår på klenare död granstam</t>
+          <t>Inspelad i fält med Audiomoth, flera inspelningar på samma ställe mellan 11-17 juni, så arten verkar stationär på lokalen.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4407,33 +4407,513 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Naturskog, barrblandskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134500384</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134617186</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>336327</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6442801</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Flera stycken observerade med kikare</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134617186</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134624565</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hönsakullen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>336374</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6442672</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Inspelad på plats med Audiomoth</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624565</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134452917</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kroppasjön, Ale-Skövde, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>336371</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6442787</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452917</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134688508</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hålan Lilla Edets kommun , Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>336247</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6442626</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gnagspår på klenare död granstam</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Naturskog, barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134688508</t>
         </is>
@@ -4473,6 +4953,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -3459,7 +3459,7 @@
         <v>134624853</v>
       </c>
       <c r="B26" t="n">
-        <v>57781</v>
+        <v>57783</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>134500384</v>
       </c>
       <c r="B33" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>134617186</v>
       </c>
       <c r="B34" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>134624565</v>
       </c>
       <c r="B35" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -3459,7 +3459,7 @@
         <v>134624853</v>
       </c>
       <c r="B26" t="n">
-        <v>57783</v>
+        <v>57784</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>134500384</v>
       </c>
       <c r="B33" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>134617186</v>
       </c>
       <c r="B34" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>134624565</v>
       </c>
       <c r="B35" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -3459,7 +3459,7 @@
         <v>134624853</v>
       </c>
       <c r="B26" t="n">
-        <v>57784</v>
+        <v>57788</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>134500384</v>
       </c>
       <c r="B33" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>134617186</v>
       </c>
       <c r="B34" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>134624565</v>
       </c>
       <c r="B35" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -3459,7 +3459,7 @@
         <v>134624853</v>
       </c>
       <c r="B26" t="n">
-        <v>57788</v>
+        <v>57789</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>134500384</v>
       </c>
       <c r="B33" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>134617186</v>
       </c>
       <c r="B34" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>134624565</v>
       </c>
       <c r="B35" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
